--- a/ig/test-tabs-svs/ValueSet-jdv-j394-type-demande-compensation-ms.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-j394-type-demande-compensation-ms.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="85">
   <si>
     <t>Property</t>
   </si>
@@ -135,9 +135,6 @@
   </si>
   <si>
     <t>warning-draft</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j394-type-demande-compensation-ms|20260505120000</t>
   </si>
   <si>
     <t>Level</t>
@@ -588,7 +585,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -620,14 +617,6 @@
         <v>39</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B5" t="s" s="2">
         <v>37</v>
       </c>
     </row>
@@ -643,40 +632,40 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>41</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>42</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>38</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>45</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>46</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>48</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>49</v>
       </c>
       <c r="F2" t="s" s="2">
         <v>15</v>
@@ -687,17 +676,17 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>51</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>15</v>
@@ -708,17 +697,17 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>53</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>15</v>
@@ -729,17 +718,17 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>55</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>15</v>
@@ -750,17 +739,17 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s" s="2">
         <v>56</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>57</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>15</v>
@@ -771,17 +760,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s" s="2">
         <v>58</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>59</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>15</v>
@@ -792,17 +781,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E8" t="s" s="2">
         <v>60</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>61</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>15</v>
@@ -813,17 +802,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s" s="2">
         <v>62</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>63</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>15</v>
@@ -834,17 +823,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>64</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>65</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>15</v>
@@ -855,17 +844,17 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>67</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>15</v>
@@ -876,17 +865,17 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>15</v>
@@ -897,17 +886,17 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E13" t="s" s="2">
         <v>70</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>71</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>15</v>
@@ -918,17 +907,17 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>15</v>
@@ -939,17 +928,17 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E15" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>15</v>
@@ -960,17 +949,17 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="E16" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>15</v>
@@ -981,17 +970,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E17" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>15</v>
@@ -1002,17 +991,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E18" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="E18" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>15</v>
@@ -1023,17 +1012,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="E19" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>15</v>
@@ -1044,17 +1033,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E20" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>15</v>
